--- a/output/yearly_total_coral_cover_iteration_12_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_12_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.27386323392653</v>
+        <v>1.258410525061685</v>
       </c>
       <c r="C3" t="n">
-        <v>4.61032343486824</v>
+        <v>4.579938343421802</v>
       </c>
       <c r="D3" t="n">
-        <v>6.076885847282323</v>
+        <v>6.054128935497882</v>
       </c>
       <c r="E3" t="n">
-        <v>11.96107251607709</v>
+        <v>11.89247780398137</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.436595777179626</v>
+        <v>1.394628047782893</v>
       </c>
       <c r="C4" t="n">
-        <v>5.082757078381007</v>
+        <v>4.978115474951348</v>
       </c>
       <c r="D4" t="n">
-        <v>6.421489816888829</v>
+        <v>6.282299015902701</v>
       </c>
       <c r="E4" t="n">
-        <v>12.94084267244946</v>
+        <v>12.65504253863694</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.646910736558119</v>
+        <v>1.581290067256317</v>
       </c>
       <c r="C5" t="n">
-        <v>5.650898816882187</v>
+        <v>5.482899024783198</v>
       </c>
       <c r="D5" t="n">
-        <v>6.803677867726161</v>
+        <v>6.666267154525555</v>
       </c>
       <c r="E5" t="n">
-        <v>14.10148742116647</v>
+        <v>13.73045624656507</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.89883002619151</v>
+        <v>1.806662955022398</v>
       </c>
       <c r="C6" t="n">
-        <v>6.321263896926068</v>
+        <v>6.079323261594036</v>
       </c>
       <c r="D6" t="n">
-        <v>7.24622639366613</v>
+        <v>6.976821017093451</v>
       </c>
       <c r="E6" t="n">
-        <v>15.46632031678371</v>
+        <v>14.86280723370989</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.186109793809738</v>
+        <v>2.065242295497217</v>
       </c>
       <c r="C7" t="n">
-        <v>7.103694586629019</v>
+        <v>6.78170268908122</v>
       </c>
       <c r="D7" t="n">
-        <v>7.688505817057385</v>
+        <v>7.310558016733223</v>
       </c>
       <c r="E7" t="n">
-        <v>16.97831019749614</v>
+        <v>16.15750300131166</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.40976163864515</v>
+        <v>1.284514432189923</v>
       </c>
       <c r="C8" t="n">
-        <v>4.707157003692171</v>
+        <v>4.426178833631048</v>
       </c>
       <c r="D8" t="n">
-        <v>6.040314064356389</v>
+        <v>5.537348378228331</v>
       </c>
       <c r="E8" t="n">
-        <v>12.15723270669371</v>
+        <v>11.2480416440493</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.797422873875005</v>
+        <v>1.618307078822994</v>
       </c>
       <c r="C9" t="n">
-        <v>5.670113580947873</v>
+        <v>5.308510437763005</v>
       </c>
       <c r="D9" t="n">
-        <v>6.604641342624212</v>
+        <v>6.105643399462586</v>
       </c>
       <c r="E9" t="n">
-        <v>14.07217779744709</v>
+        <v>13.03246091604858</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.213355387991582</v>
+        <v>1.981027777635831</v>
       </c>
       <c r="C10" t="n">
-        <v>6.799198732407653</v>
+        <v>6.354063096194974</v>
       </c>
       <c r="D10" t="n">
-        <v>7.153078445360399</v>
+        <v>6.640372929560065</v>
       </c>
       <c r="E10" t="n">
-        <v>16.16563256575963</v>
+        <v>14.97546380339087</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.63475804969087</v>
+        <v>2.36831328452651</v>
       </c>
       <c r="C11" t="n">
-        <v>8.100977531068915</v>
+        <v>7.532789404726358</v>
       </c>
       <c r="D11" t="n">
-        <v>7.702500429104735</v>
+        <v>7.194375653490017</v>
       </c>
       <c r="E11" t="n">
-        <v>18.43823600986452</v>
+        <v>17.09547834274289</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.069196557802371</v>
+        <v>2.768054116376137</v>
       </c>
       <c r="C12" t="n">
-        <v>9.503677104601156</v>
+        <v>8.871386958164633</v>
       </c>
       <c r="D12" t="n">
-        <v>8.310607399218704</v>
+        <v>7.702427731861877</v>
       </c>
       <c r="E12" t="n">
-        <v>20.88348106162223</v>
+        <v>19.34186880640265</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.498173086656404</v>
+        <v>3.171523369209136</v>
       </c>
       <c r="C13" t="n">
-        <v>10.97990476956123</v>
+        <v>10.3144047134316</v>
       </c>
       <c r="D13" t="n">
-        <v>8.871545760600387</v>
+        <v>8.234590362909978</v>
       </c>
       <c r="E13" t="n">
-        <v>23.34962361681802</v>
+        <v>21.72051844555072</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.012425714073282</v>
+        <v>1.84523408004005</v>
       </c>
       <c r="C14" t="n">
-        <v>7.793486340438794</v>
+        <v>7.378580125670007</v>
       </c>
       <c r="D14" t="n">
-        <v>6.692888259115865</v>
+        <v>6.281909035164066</v>
       </c>
       <c r="E14" t="n">
-        <v>16.49880031362794</v>
+        <v>15.50572324087412</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.092634501510246</v>
+        <v>1.920504676524653</v>
       </c>
       <c r="C15" t="n">
-        <v>8.469252737703002</v>
+        <v>8.070604264916541</v>
       </c>
       <c r="D15" t="n">
-        <v>6.766332804870569</v>
+        <v>6.325940419699536</v>
       </c>
       <c r="E15" t="n">
-        <v>17.32822004408382</v>
+        <v>16.31704936114073</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.458914752487689</v>
+        <v>2.270703900106533</v>
       </c>
       <c r="C16" t="n">
-        <v>10.04893388122133</v>
+        <v>9.664893814274064</v>
       </c>
       <c r="D16" t="n">
-        <v>7.377765275075483</v>
+        <v>6.820662722823588</v>
       </c>
       <c r="E16" t="n">
-        <v>19.88561390878451</v>
+        <v>18.75626043720419</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.990434565498153</v>
+        <v>1.84678524141276</v>
       </c>
       <c r="C17" t="n">
-        <v>9.334044837942889</v>
+        <v>9.097198204293347</v>
       </c>
       <c r="D17" t="n">
-        <v>6.906928893595755</v>
+        <v>6.355677557661171</v>
       </c>
       <c r="E17" t="n">
-        <v>18.2314082970368</v>
+        <v>17.29966100336728</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.284212748516969</v>
+        <v>2.150390718951086</v>
       </c>
       <c r="C18" t="n">
-        <v>10.90523386381948</v>
+        <v>10.73688376749524</v>
       </c>
       <c r="D18" t="n">
-        <v>7.40703117413908</v>
+        <v>6.82592489051835</v>
       </c>
       <c r="E18" t="n">
-        <v>20.59647778647553</v>
+        <v>19.71319937696468</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.301736945037774</v>
+        <v>2.195070056971358</v>
       </c>
       <c r="C19" t="n">
-        <v>11.68065747054179</v>
+        <v>11.60401242727124</v>
       </c>
       <c r="D19" t="n">
-        <v>7.546321538417618</v>
+        <v>6.934408011837624</v>
       </c>
       <c r="E19" t="n">
-        <v>21.52871595399718</v>
+        <v>20.73349049608022</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.576803016813646</v>
+        <v>2.47260031548489</v>
       </c>
       <c r="C20" t="n">
-        <v>13.47030499556738</v>
+        <v>13.46529808227572</v>
       </c>
       <c r="D20" t="n">
-        <v>8.072175061243337</v>
+        <v>7.422709684975902</v>
       </c>
       <c r="E20" t="n">
-        <v>24.11928307362436</v>
+        <v>23.36060808273651</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.535492679350182</v>
+        <v>1.489487981929176</v>
       </c>
       <c r="C21" t="n">
-        <v>9.919775153250622</v>
+        <v>9.994122906893233</v>
       </c>
       <c r="D21" t="n">
-        <v>6.769062063488376</v>
+        <v>6.200198173739603</v>
       </c>
       <c r="E21" t="n">
-        <v>18.22432989608918</v>
+        <v>17.68380906256201</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_12_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_12_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.258410525061685</v>
+        <v>1.247051704123549</v>
       </c>
       <c r="C3" t="n">
-        <v>4.579938343421802</v>
+        <v>4.608467931707214</v>
       </c>
       <c r="D3" t="n">
-        <v>6.054128935497882</v>
+        <v>6.214526875417725</v>
       </c>
       <c r="E3" t="n">
-        <v>11.89247780398137</v>
+        <v>12.07004651124849</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.394628047782893</v>
+        <v>1.357605313039357</v>
       </c>
       <c r="C4" t="n">
-        <v>4.978115474951348</v>
+        <v>5.09850469726</v>
       </c>
       <c r="D4" t="n">
-        <v>6.282299015902701</v>
+        <v>6.628292773281285</v>
       </c>
       <c r="E4" t="n">
-        <v>12.65504253863694</v>
+        <v>13.08440278358064</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.581290067256317</v>
+        <v>1.511488982088165</v>
       </c>
       <c r="C5" t="n">
-        <v>5.482899024783198</v>
+        <v>5.771539930751732</v>
       </c>
       <c r="D5" t="n">
-        <v>6.666267154525555</v>
+        <v>7.015195004181839</v>
       </c>
       <c r="E5" t="n">
-        <v>13.73045624656507</v>
+        <v>14.29822391702174</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.806662955022398</v>
+        <v>1.693966317655392</v>
       </c>
       <c r="C6" t="n">
-        <v>6.079323261594036</v>
+        <v>6.640926834075904</v>
       </c>
       <c r="D6" t="n">
-        <v>6.976821017093451</v>
+        <v>7.49277945396868</v>
       </c>
       <c r="E6" t="n">
-        <v>14.86280723370989</v>
+        <v>15.82767260569998</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.065242295497217</v>
+        <v>1.895519531781552</v>
       </c>
       <c r="C7" t="n">
-        <v>6.78170268908122</v>
+        <v>7.722532004971105</v>
       </c>
       <c r="D7" t="n">
-        <v>7.310558016733223</v>
+        <v>7.966185690536178</v>
       </c>
       <c r="E7" t="n">
-        <v>16.15750300131166</v>
+        <v>17.58423722728883</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.284514432189923</v>
+        <v>1.135193480783482</v>
       </c>
       <c r="C8" t="n">
-        <v>4.426178833631048</v>
+        <v>5.531218578664079</v>
       </c>
       <c r="D8" t="n">
-        <v>5.537348378228331</v>
+        <v>6.163355995429922</v>
       </c>
       <c r="E8" t="n">
-        <v>11.2480416440493</v>
+        <v>12.82976805487748</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.618307078822994</v>
+        <v>1.398728585210762</v>
       </c>
       <c r="C9" t="n">
-        <v>5.308510437763005</v>
+        <v>6.914731176834475</v>
       </c>
       <c r="D9" t="n">
-        <v>6.105643399462586</v>
+        <v>6.708311445084725</v>
       </c>
       <c r="E9" t="n">
-        <v>13.03246091604858</v>
+        <v>15.02177120712996</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.981027777635831</v>
+        <v>1.670044206565001</v>
       </c>
       <c r="C10" t="n">
-        <v>6.354063096194974</v>
+        <v>8.455937222207185</v>
       </c>
       <c r="D10" t="n">
-        <v>6.640372929560065</v>
+        <v>7.226876963290958</v>
       </c>
       <c r="E10" t="n">
-        <v>14.97546380339087</v>
+        <v>17.35285839206314</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.36831328452651</v>
+        <v>1.93716317081871</v>
       </c>
       <c r="C11" t="n">
-        <v>7.532789404726358</v>
+        <v>10.07013051198435</v>
       </c>
       <c r="D11" t="n">
-        <v>7.194375653490017</v>
+        <v>7.80692470226292</v>
       </c>
       <c r="E11" t="n">
-        <v>17.09547834274289</v>
+        <v>19.81421838506598</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.768054116376137</v>
+        <v>2.194952668102917</v>
       </c>
       <c r="C12" t="n">
-        <v>8.871386958164633</v>
+        <v>11.70686818965927</v>
       </c>
       <c r="D12" t="n">
-        <v>7.702427731861877</v>
+        <v>8.373932872191496</v>
       </c>
       <c r="E12" t="n">
-        <v>19.34186880640265</v>
+        <v>22.27575372995368</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.171523369209136</v>
+        <v>2.432988679238554</v>
       </c>
       <c r="C13" t="n">
-        <v>10.3144047134316</v>
+        <v>13.31326060923525</v>
       </c>
       <c r="D13" t="n">
-        <v>8.234590362909978</v>
+        <v>8.958729953872885</v>
       </c>
       <c r="E13" t="n">
-        <v>21.72051844555072</v>
+        <v>24.70497924234669</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84523408004005</v>
+        <v>1.396437934520663</v>
       </c>
       <c r="C14" t="n">
-        <v>7.378580125670007</v>
+        <v>9.177858595674264</v>
       </c>
       <c r="D14" t="n">
-        <v>6.281909035164066</v>
+        <v>6.734671441408609</v>
       </c>
       <c r="E14" t="n">
-        <v>15.50572324087412</v>
+        <v>17.30896797160354</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.920504676524653</v>
+        <v>1.40672665046117</v>
       </c>
       <c r="C15" t="n">
-        <v>8.070604264916541</v>
+        <v>9.832674496929844</v>
       </c>
       <c r="D15" t="n">
-        <v>6.325940419699536</v>
+        <v>6.786164108496354</v>
       </c>
       <c r="E15" t="n">
-        <v>16.31704936114073</v>
+        <v>18.02556525588737</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.270703900106533</v>
+        <v>1.613983408304714</v>
       </c>
       <c r="C16" t="n">
-        <v>9.664893814274064</v>
+        <v>11.5562896713678</v>
       </c>
       <c r="D16" t="n">
-        <v>6.820662722823588</v>
+        <v>7.317829577731216</v>
       </c>
       <c r="E16" t="n">
-        <v>18.75626043720419</v>
+        <v>20.48810265740373</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.84678524141276</v>
+        <v>1.285421904124434</v>
       </c>
       <c r="C17" t="n">
-        <v>9.097198204293347</v>
+        <v>10.57510156331241</v>
       </c>
       <c r="D17" t="n">
-        <v>6.355677557661171</v>
+        <v>6.837293528933529</v>
       </c>
       <c r="E17" t="n">
-        <v>17.29966100336728</v>
+        <v>18.69781699637037</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.150390718951086</v>
+        <v>1.457119760120159</v>
       </c>
       <c r="C18" t="n">
-        <v>10.73688376749524</v>
+        <v>12.29014608029229</v>
       </c>
       <c r="D18" t="n">
-        <v>6.82592489051835</v>
+        <v>7.301807455197908</v>
       </c>
       <c r="E18" t="n">
-        <v>19.71319937696468</v>
+        <v>21.04907329561036</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.195070056971358</v>
+        <v>1.450728582565512</v>
       </c>
       <c r="C19" t="n">
-        <v>11.60401242727124</v>
+        <v>13.11465707222693</v>
       </c>
       <c r="D19" t="n">
-        <v>6.934408011837624</v>
+        <v>7.40492041657495</v>
       </c>
       <c r="E19" t="n">
-        <v>20.73349049608022</v>
+        <v>21.9703060713674</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.47260031548489</v>
+        <v>1.602879841769683</v>
       </c>
       <c r="C20" t="n">
-        <v>13.46529808227572</v>
+        <v>15.15041892923016</v>
       </c>
       <c r="D20" t="n">
-        <v>7.422709684975902</v>
+        <v>7.84422306179427</v>
       </c>
       <c r="E20" t="n">
-        <v>23.36060808273651</v>
+        <v>24.59752183279411</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.489487981929176</v>
+        <v>0.9493107600984958</v>
       </c>
       <c r="C21" t="n">
-        <v>9.994122906893233</v>
+        <v>11.21436658093272</v>
       </c>
       <c r="D21" t="n">
-        <v>6.200198173739603</v>
+        <v>6.549454919525407</v>
       </c>
       <c r="E21" t="n">
-        <v>17.68380906256201</v>
+        <v>18.71313226055662</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_12_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_12_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.247051704123549</v>
+        <v>2.598793687272304</v>
       </c>
       <c r="C3" t="n">
-        <v>4.608467931707214</v>
+        <v>7.729944798376447</v>
       </c>
       <c r="D3" t="n">
-        <v>6.214526875417725</v>
+        <v>8.150143268972039</v>
       </c>
       <c r="E3" t="n">
-        <v>12.07004651124849</v>
+        <v>18.47888175462079</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.357605313039357</v>
+        <v>1.09056683047706</v>
       </c>
       <c r="C4" t="n">
-        <v>5.09850469726</v>
+        <v>4.595876693584172</v>
       </c>
       <c r="D4" t="n">
-        <v>6.628292773281285</v>
+        <v>5.880875062835721</v>
       </c>
       <c r="E4" t="n">
-        <v>13.08440278358064</v>
+        <v>11.56731858689695</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.511488982088165</v>
+        <v>1.200913793517744</v>
       </c>
       <c r="C5" t="n">
-        <v>5.771539930751732</v>
+        <v>5.390278757886216</v>
       </c>
       <c r="D5" t="n">
-        <v>7.015195004181839</v>
+        <v>6.233693759003718</v>
       </c>
       <c r="E5" t="n">
-        <v>14.29822391702174</v>
+        <v>12.82488631040768</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.693966317655392</v>
+        <v>1.317730947030896</v>
       </c>
       <c r="C6" t="n">
-        <v>6.640926834075904</v>
+        <v>6.421891554027392</v>
       </c>
       <c r="D6" t="n">
-        <v>7.49277945396868</v>
+        <v>6.657854546616434</v>
       </c>
       <c r="E6" t="n">
-        <v>15.82767260569998</v>
+        <v>14.39747704767472</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.895519531781552</v>
+        <v>1.44361074423818</v>
       </c>
       <c r="C7" t="n">
-        <v>7.722532004971105</v>
+        <v>7.627655703267167</v>
       </c>
       <c r="D7" t="n">
-        <v>7.966185690536178</v>
+        <v>7.066873127477206</v>
       </c>
       <c r="E7" t="n">
-        <v>17.58423722728883</v>
+        <v>16.13813957498255</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.135193480783482</v>
+        <v>1.587534401467995</v>
       </c>
       <c r="C8" t="n">
-        <v>5.531218578664079</v>
+        <v>8.959960843070682</v>
       </c>
       <c r="D8" t="n">
-        <v>6.163355995429922</v>
+        <v>7.625882191448702</v>
       </c>
       <c r="E8" t="n">
-        <v>12.82976805487748</v>
+        <v>18.17337743598738</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.398728585210762</v>
+        <v>1.725874768008243</v>
       </c>
       <c r="C9" t="n">
-        <v>6.914731176834475</v>
+        <v>10.41296434157458</v>
       </c>
       <c r="D9" t="n">
-        <v>6.708311445084725</v>
+        <v>8.158511408257661</v>
       </c>
       <c r="E9" t="n">
-        <v>15.02177120712996</v>
+        <v>20.29735051784049</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.670044206565001</v>
+        <v>1.079775212515854</v>
       </c>
       <c r="C10" t="n">
-        <v>8.455937222207185</v>
+        <v>7.494151465413943</v>
       </c>
       <c r="D10" t="n">
-        <v>7.226876963290958</v>
+        <v>6.439106477568065</v>
       </c>
       <c r="E10" t="n">
-        <v>17.35285839206314</v>
+        <v>15.01303315549786</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.93716317081871</v>
+        <v>1.028783236757275</v>
       </c>
       <c r="C11" t="n">
-        <v>10.07013051198435</v>
+        <v>8.082561951954268</v>
       </c>
       <c r="D11" t="n">
-        <v>7.80692470226292</v>
+        <v>6.394662758996811</v>
       </c>
       <c r="E11" t="n">
-        <v>19.81421838506598</v>
+        <v>15.50600794770835</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.194952668102917</v>
+        <v>1.11416583459562</v>
       </c>
       <c r="C12" t="n">
-        <v>11.70686818965927</v>
+        <v>9.584557399635548</v>
       </c>
       <c r="D12" t="n">
-        <v>8.373932872191496</v>
+        <v>6.894931936649859</v>
       </c>
       <c r="E12" t="n">
-        <v>22.27575372995368</v>
+        <v>17.59365517088103</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.432988679238554</v>
+        <v>0.8849866505162448</v>
       </c>
       <c r="C13" t="n">
-        <v>13.31326060923525</v>
+        <v>9.105729591843252</v>
       </c>
       <c r="D13" t="n">
-        <v>8.958729953872885</v>
+        <v>6.388948987358096</v>
       </c>
       <c r="E13" t="n">
-        <v>24.70497924234669</v>
+        <v>16.37966522971759</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.396437934520663</v>
+        <v>0.9622403773634264</v>
       </c>
       <c r="C14" t="n">
-        <v>9.177858595674264</v>
+        <v>10.63969074477481</v>
       </c>
       <c r="D14" t="n">
-        <v>6.734671441408609</v>
+        <v>6.875728951554792</v>
       </c>
       <c r="E14" t="n">
-        <v>17.30896797160354</v>
+        <v>18.47766007369303</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.40672665046117</v>
+        <v>0.934545274626624</v>
       </c>
       <c r="C15" t="n">
-        <v>9.832674496929844</v>
+        <v>11.45736877268789</v>
       </c>
       <c r="D15" t="n">
-        <v>6.786164108496354</v>
+        <v>7.00142211012951</v>
       </c>
       <c r="E15" t="n">
-        <v>18.02556525588737</v>
+        <v>19.39333615744403</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.613983408304714</v>
+        <v>1.022303701909246</v>
       </c>
       <c r="C16" t="n">
-        <v>11.5562896713678</v>
+        <v>13.27764682608599</v>
       </c>
       <c r="D16" t="n">
-        <v>7.317829577731216</v>
+        <v>7.469735400009324</v>
       </c>
       <c r="E16" t="n">
-        <v>20.48810265740373</v>
+        <v>21.76968592800456</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.285421904124434</v>
+        <v>0.6098813088322036</v>
       </c>
       <c r="C17" t="n">
-        <v>10.57510156331241</v>
+        <v>9.863727176815173</v>
       </c>
       <c r="D17" t="n">
-        <v>6.837293528933529</v>
+        <v>6.267222089508533</v>
       </c>
       <c r="E17" t="n">
-        <v>18.69781699637037</v>
+        <v>16.74083057515591</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.457119760120159</v>
+        <v>0.4931907767054277</v>
       </c>
       <c r="C18" t="n">
-        <v>12.29014608029229</v>
+        <v>8.780152600683882</v>
       </c>
       <c r="D18" t="n">
-        <v>7.301807455197908</v>
+        <v>5.804131697415313</v>
       </c>
       <c r="E18" t="n">
-        <v>21.04907329561036</v>
+        <v>15.07747507480462</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.450728582565512</v>
+        <v>0.5787991765157496</v>
       </c>
       <c r="C19" t="n">
-        <v>13.11465707222693</v>
+        <v>10.8330655900803</v>
       </c>
       <c r="D19" t="n">
-        <v>7.40492041657495</v>
+        <v>6.367792324331577</v>
       </c>
       <c r="E19" t="n">
-        <v>21.9703060713674</v>
+        <v>17.77965709092763</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.602879841769683</v>
+        <v>0.6573782627636643</v>
       </c>
       <c r="C20" t="n">
-        <v>15.15041892923016</v>
+        <v>12.98076632032175</v>
       </c>
       <c r="D20" t="n">
-        <v>7.84422306179427</v>
+        <v>6.89397964137674</v>
       </c>
       <c r="E20" t="n">
-        <v>24.59752183279411</v>
+        <v>20.53212422446216</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9493107600984958</v>
+        <v>0.7248832349076749</v>
       </c>
       <c r="C21" t="n">
-        <v>11.21436658093272</v>
+        <v>15.26502815622393</v>
       </c>
       <c r="D21" t="n">
-        <v>6.549454919525407</v>
+        <v>7.405214940886224</v>
       </c>
       <c r="E21" t="n">
-        <v>18.71313226055662</v>
+        <v>23.39512633201783</v>
       </c>
     </row>
   </sheetData>
